--- a/Tax_AI_題庫管理範本.xlsx
+++ b/Tax_AI_題庫管理範本.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Profiles\113604.TRS\Downloads\Tax_AI_縮圖與四格漫畫版\Tax_AI_縮圖與四格漫畫版\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Profiles\113604.TRS\Downloads\Tax_AI_縮圖與四格漫畫版_修復版\Tax_AI_縮圖與四格漫畫版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E752887-57F3-457A-ADC7-57D4CCFE1DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868CDFD8-DEEA-448D-9014-31EDA1ADA0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31255,7 +31255,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuestionBankTable" displayName="QuestionBankTable" ref="A1:J200">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuestionBankTable" displayName="QuestionBankTable" ref="A1:J199">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="編號"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分類"/>
@@ -31421,7 +31421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N200"/>
+  <dimension ref="A1:N199"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -36345,17 +36345,6 @@
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
     </row>
-    <row r="200" spans="1:9">
-      <c r="A200" s="3"/>
-      <c r="B200" s="3"/>
-      <c r="C200" s="2"/>
-      <c r="D200" s="2"/>
-      <c r="E200" s="2"/>
-      <c r="F200" s="2"/>
-      <c r="G200" s="3"/>
-      <c r="H200" s="2"/>
-      <c r="I200" s="2"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36369,13 +36358,13 @@
           <x14:formula1>
             <xm:f>選單!$A$2:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B200</xm:sqref>
+          <xm:sqref>B2:B199</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BA06DD53-D9A2-45DB-B1DB-54BA1E025838}">
           <x14:formula1>
             <xm:f>選單!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G200</xm:sqref>
+          <xm:sqref>G2:G199</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
